--- a/NECP Scenario/Results/Regional Results/KARPATHOS_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/KARPATHOS_Capacity.xlsx
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.235046822852797E-08</v>
+        <v>4.780606455337349E-08</v>
       </c>
       <c r="C3">
-        <v>3.250641601402858E-08</v>
+        <v>4.804102349969775E-08</v>
       </c>
       <c r="D3">
-        <v>0.0050826930904559</v>
+        <v>0.0050826989991487</v>
       </c>
       <c r="E3">
-        <v>0.2889237682071111</v>
+        <v>0.3413470837613917</v>
       </c>
       <c r="F3">
-        <v>0.2895472173294425</v>
+        <v>0.3413470471207811</v>
       </c>
       <c r="G3">
-        <v>0.2844645642743086</v>
+        <v>0.3393981269206215</v>
       </c>
       <c r="H3">
-        <v>0.2929240477069434</v>
+        <v>0.3485228572844909</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.4000000000065533</v>
+        <v>0.4000000000070409</v>
       </c>
       <c r="C13">
-        <v>0.400000000008596</v>
+        <v>0.4000000000100411</v>
       </c>
       <c r="D13">
-        <v>0.4000000000127148</v>
+        <v>0.4000000000157641</v>
       </c>
       <c r="E13">
-        <v>0.4000000000234099</v>
+        <v>0.4000000000288374</v>
       </c>
       <c r="F13">
-        <v>0.4000000000404743</v>
+        <v>0.4000000000494614</v>
       </c>
       <c r="G13">
-        <v>0.4000000000745182</v>
+        <v>0.400000000094562</v>
       </c>
       <c r="H13">
-        <v>0.4000000004248863</v>
+        <v>0.4000000005048099</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1163,19 +1163,19 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0.0176196565384901</v>
+        <v>0.0176196210000725</v>
       </c>
       <c r="E27">
-        <v>0.0568753950411807</v>
+        <v>0.0573398341402329</v>
       </c>
       <c r="F27">
-        <v>0.07343654507107809</v>
+        <v>0.08310693459212951</v>
       </c>
       <c r="G27">
-        <v>0.1308464149269715</v>
+        <v>0.1305258513920963</v>
       </c>
       <c r="H27">
-        <v>0.1555233895603547</v>
+        <v>0.1555233891568926</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1215,19 +1215,19 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>4.063509394123365E-08</v>
+        <v>6.005300914804575E-08</v>
       </c>
       <c r="E29">
-        <v>0.008716334700575401</v>
+        <v>0.009172487582858799</v>
       </c>
       <c r="F29">
-        <v>0.0108884609775382</v>
+        <v>0.0110997726790287</v>
       </c>
       <c r="G29">
-        <v>0.0110997837488623</v>
+        <v>0.011099783646703</v>
       </c>
       <c r="H29">
-        <v>0.0110997838956899</v>
+        <v>0.0110997838524506</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1319,19 +1319,19 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0.0090299031477274</v>
+        <v>0.0090299030471326</v>
       </c>
       <c r="E33">
-        <v>0.2997240061203766</v>
+        <v>0.299108302596287</v>
       </c>
       <c r="F33">
-        <v>0.3035644199240159</v>
+        <v>0.3026914208693098</v>
       </c>
       <c r="G33">
-        <v>0.3044147469233143</v>
+        <v>0.3036722325944211</v>
       </c>
       <c r="H33">
-        <v>0.3135214722137756</v>
+        <v>0.3137714713539016</v>
       </c>
     </row>
     <row r="34" spans="1:8">
